--- a/outputs/daily/hr_rankings_2026-08-08.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-08.xlsx
@@ -6102,34 +6102,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8050,34 +8046,30 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9438,34 +9430,30 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -11384,28 +11372,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y40" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11662,34 +11654,30 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -15810,34 +15798,30 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18300,28 +18284,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y65" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -35154,34 +35142,30 @@
       </c>
       <c r="W126" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -47588,28 +47572,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W171" t="inlineStr"/>
-      <c r="X171" t="inlineStr"/>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y171" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB171" t="inlineStr"/>
       <c r="AC171" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -78512,34 +78500,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-08-08.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-08.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
